--- a/artfynd/A 59295-2023 artfynd.xlsx
+++ b/artfynd/A 59295-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 59295-2023 artfynd.xlsx
+++ b/artfynd/A 59295-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -779,6 +779,765 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>114876997</v>
+      </c>
+      <c r="B3" t="n">
+        <v>57235</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Sörträsket, Vinliden, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>641298</v>
+      </c>
+      <c r="R3" t="n">
+        <v>7174666</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2024-02-25</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2024-02-25</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Via Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>114876994</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57235</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Sörträsket, Vinliden, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>641386</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7174670</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2024-02-25</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2024-02-25</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Via Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>114877006</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57235</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Sörträsket, Vinliden, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>641096</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7174648</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-02-25</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-02-25</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Via Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>114876996</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57235</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Sörträsket, Vinliden, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>641363</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7174666</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-02-25</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-02-25</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>två träd</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Via Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>114877008</v>
+      </c>
+      <c r="B7" t="n">
+        <v>57235</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Sörträsket, Vinliden, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>641238</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7174621</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-02-25</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-02-25</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Via Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>114876999</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57235</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Sörträsket, Vinliden, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>641228</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7174682</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2024-02-25</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2024-02-25</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Via Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>114876998</v>
+      </c>
+      <c r="B9" t="n">
+        <v>57235</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Sörträsket, Vinliden, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>641231</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7174683</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2024-02-25</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2024-02-25</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>tre träd</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Via Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 59295-2023 artfynd.xlsx
+++ b/artfynd/A 59295-2023 artfynd.xlsx
@@ -1541,10 +1541,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119536290</v>
+        <v>119536065</v>
       </c>
       <c r="B10" t="n">
-        <v>90509</v>
+        <v>57310</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1557,34 +1557,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>112</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Hållängestjärnen, Ly lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>641323</v>
+        <v>641222</v>
       </c>
       <c r="R10" t="n">
-        <v>7174811</v>
+        <v>7174563</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1616,7 +1621,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1626,7 +1631,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1653,10 +1658,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119536694</v>
+        <v>119536244</v>
       </c>
       <c r="B11" t="n">
-        <v>79643</v>
+        <v>91886</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1665,25 +1670,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6464</v>
+        <v>232140</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tajgataggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Phellodon secretus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>Niemelä &amp; Kinnunen</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1693,10 +1698,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>641286</v>
+        <v>641086</v>
       </c>
       <c r="R11" t="n">
-        <v>7174838</v>
+        <v>7174359</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1728,7 +1733,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1738,7 +1743,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1765,10 +1770,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119536065</v>
+        <v>119536290</v>
       </c>
       <c r="B12" t="n">
-        <v>57310</v>
+        <v>90509</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1781,39 +1786,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>112</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Hållängestjärnen, Ly lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>641222</v>
+        <v>641323</v>
       </c>
       <c r="R12" t="n">
-        <v>7174563</v>
+        <v>7174811</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1845,7 +1845,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1855,7 +1855,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1882,10 +1882,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119536244</v>
+        <v>119536694</v>
       </c>
       <c r="B13" t="n">
-        <v>91886</v>
+        <v>79643</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1894,25 +1894,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>232140</v>
+        <v>6464</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tajgataggsvamp</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellodon secretus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Niemelä &amp; Kinnunen</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1922,10 +1922,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>641086</v>
+        <v>641286</v>
       </c>
       <c r="R13" t="n">
-        <v>7174359</v>
+        <v>7174838</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1957,7 +1957,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1967,7 +1967,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -3236,10 +3236,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119535988</v>
+        <v>119536264</v>
       </c>
       <c r="B25" t="n">
-        <v>90527</v>
+        <v>91884</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3248,25 +3248,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5447</v>
+        <v>5449</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3276,10 +3276,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>641115</v>
+        <v>641091</v>
       </c>
       <c r="R25" t="n">
-        <v>7174359</v>
+        <v>7174366</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3311,7 +3311,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3348,10 +3348,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119536264</v>
+        <v>119535988</v>
       </c>
       <c r="B26" t="n">
-        <v>91884</v>
+        <v>90527</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3360,25 +3360,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5449</v>
+        <v>5447</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3388,10 +3388,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>641091</v>
+        <v>641115</v>
       </c>
       <c r="R26" t="n">
-        <v>7174366</v>
+        <v>7174359</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3423,7 +3423,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3433,7 +3433,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -4024,10 +4024,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119536611</v>
+        <v>119536693</v>
       </c>
       <c r="B32" t="n">
-        <v>91832</v>
+        <v>79643</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4036,25 +4036,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4361</v>
+        <v>6464</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4064,10 +4064,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>641078</v>
+        <v>641308</v>
       </c>
       <c r="R32" t="n">
-        <v>7174380</v>
+        <v>7174808</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -4099,7 +4099,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4109,7 +4109,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4136,10 +4136,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119536693</v>
+        <v>119536611</v>
       </c>
       <c r="B33" t="n">
-        <v>79643</v>
+        <v>91832</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4148,25 +4148,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6464</v>
+        <v>4361</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4176,10 +4176,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>641308</v>
+        <v>641078</v>
       </c>
       <c r="R33" t="n">
-        <v>7174808</v>
+        <v>7174380</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4211,7 +4211,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4221,7 +4221,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4706,10 +4706,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119537107</v>
+        <v>119536234</v>
       </c>
       <c r="B38" t="n">
-        <v>91840</v>
+        <v>91463</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4718,25 +4718,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>4364</v>
+        <v>4745</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4746,10 +4746,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>641119</v>
+        <v>641099</v>
       </c>
       <c r="R38" t="n">
-        <v>7174434</v>
+        <v>7174354</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4781,7 +4781,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4791,7 +4791,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4818,10 +4818,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119536234</v>
+        <v>119537107</v>
       </c>
       <c r="B39" t="n">
-        <v>91463</v>
+        <v>91840</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4830,25 +4830,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>4745</v>
+        <v>4364</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4858,10 +4858,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>641099</v>
+        <v>641119</v>
       </c>
       <c r="R39" t="n">
-        <v>7174354</v>
+        <v>7174434</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4893,7 +4893,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4903,7 +4903,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5042,10 +5042,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119536322</v>
+        <v>119536233</v>
       </c>
       <c r="B41" t="n">
-        <v>91856</v>
+        <v>91463</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5058,21 +5058,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>2059</v>
+        <v>4745</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5082,10 +5082,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>641113</v>
+        <v>641089</v>
       </c>
       <c r="R41" t="n">
-        <v>7174347</v>
+        <v>7174407</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -5117,7 +5117,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5127,7 +5127,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5154,10 +5154,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>119536233</v>
+        <v>119536075</v>
       </c>
       <c r="B42" t="n">
-        <v>91463</v>
+        <v>57310</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5170,34 +5170,39 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>4745</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Hållängestjärnen, Ly lm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>641089</v>
+        <v>641329</v>
       </c>
       <c r="R42" t="n">
-        <v>7174407</v>
+        <v>7174806</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -5229,7 +5234,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5239,7 +5244,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5266,7 +5271,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>119536075</v>
+        <v>119536066</v>
       </c>
       <c r="B43" t="n">
         <v>57310</v>
@@ -5302,7 +5307,7 @@
       <c r="I43" t="inlineStr"/>
       <c r="M43" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
@@ -5311,10 +5316,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>641329</v>
+        <v>641236</v>
       </c>
       <c r="R43" t="n">
-        <v>7174806</v>
+        <v>7174632</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -5346,7 +5351,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5356,7 +5361,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5383,10 +5388,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>119536066</v>
+        <v>119536322</v>
       </c>
       <c r="B44" t="n">
-        <v>57310</v>
+        <v>91856</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5399,39 +5404,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>2059</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Hållängestjärnen, Ly lm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>641236</v>
+        <v>641113</v>
       </c>
       <c r="R44" t="n">
-        <v>7174632</v>
+        <v>7174347</v>
       </c>
       <c r="S44" t="n">
         <v>25</v>
@@ -5463,7 +5463,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5473,7 +5473,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6070,10 +6070,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>119536073</v>
+        <v>119536652</v>
       </c>
       <c r="B50" t="n">
-        <v>57310</v>
+        <v>79607</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6086,39 +6086,34 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Hållängestjärnen, Ly lm</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>641246</v>
+        <v>641308</v>
       </c>
       <c r="R50" t="n">
-        <v>7174787</v>
+        <v>7174808</v>
       </c>
       <c r="S50" t="n">
         <v>25</v>
@@ -6150,7 +6145,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6160,7 +6155,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6187,10 +6182,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>119535981</v>
+        <v>119536073</v>
       </c>
       <c r="B51" t="n">
-        <v>58022</v>
+        <v>57310</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6203,31 +6198,27 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>103056</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Videsparv</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Emberiza rustica</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Pallas, 1776</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="M51" t="inlineStr">
         <is>
-          <t>sträckande</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
@@ -6236,10 +6227,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>640956</v>
+        <v>641246</v>
       </c>
       <c r="R51" t="n">
-        <v>7174454</v>
+        <v>7174787</v>
       </c>
       <c r="S51" t="n">
         <v>25</v>
@@ -6271,7 +6262,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6281,7 +6272,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6308,10 +6299,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>119536652</v>
+        <v>119536245</v>
       </c>
       <c r="B52" t="n">
-        <v>79607</v>
+        <v>91886</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6320,25 +6311,25 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6458</v>
+        <v>232140</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tajgataggsvamp</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellodon secretus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Niemelä &amp; Kinnunen</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6348,10 +6339,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>641308</v>
+        <v>641090</v>
       </c>
       <c r="R52" t="n">
-        <v>7174808</v>
+        <v>7174359</v>
       </c>
       <c r="S52" t="n">
         <v>25</v>
@@ -6383,7 +6374,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6393,7 +6384,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6420,10 +6411,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>119536245</v>
+        <v>119535981</v>
       </c>
       <c r="B53" t="n">
-        <v>91886</v>
+        <v>58022</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6432,38 +6423,47 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>232140</v>
+        <v>103056</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tajgataggsvamp</t>
+          <t>Videsparv</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Phellodon secretus</t>
+          <t>Emberiza rustica</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Niemelä &amp; Kinnunen</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
+          <t>Pallas, 1776</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>sträckande</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Hållängestjärnen, Ly lm</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>641090</v>
+        <v>640956</v>
       </c>
       <c r="R53" t="n">
-        <v>7174359</v>
+        <v>7174454</v>
       </c>
       <c r="S53" t="n">
         <v>25</v>
@@ -6495,7 +6495,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6505,7 +6505,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD53" t="b">

--- a/artfynd/A 59295-2023 artfynd.xlsx
+++ b/artfynd/A 59295-2023 artfynd.xlsx
@@ -4706,10 +4706,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119536234</v>
+        <v>119537107</v>
       </c>
       <c r="B38" t="n">
-        <v>91463</v>
+        <v>91840</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4718,25 +4718,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>4745</v>
+        <v>4364</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4746,10 +4746,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>641099</v>
+        <v>641119</v>
       </c>
       <c r="R38" t="n">
-        <v>7174354</v>
+        <v>7174434</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4781,7 +4781,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4791,7 +4791,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4818,10 +4818,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119537107</v>
+        <v>119536234</v>
       </c>
       <c r="B39" t="n">
-        <v>91840</v>
+        <v>91463</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4830,25 +4830,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>4364</v>
+        <v>4745</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4858,10 +4858,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>641119</v>
+        <v>641099</v>
       </c>
       <c r="R39" t="n">
-        <v>7174434</v>
+        <v>7174354</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4893,7 +4893,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4903,7 +4903,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5042,10 +5042,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119536233</v>
+        <v>119536322</v>
       </c>
       <c r="B41" t="n">
-        <v>91463</v>
+        <v>91856</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5058,21 +5058,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>4745</v>
+        <v>2059</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5082,10 +5082,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>641089</v>
+        <v>641113</v>
       </c>
       <c r="R41" t="n">
-        <v>7174407</v>
+        <v>7174347</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -5117,7 +5117,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5127,7 +5127,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5154,10 +5154,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>119536075</v>
+        <v>119536233</v>
       </c>
       <c r="B42" t="n">
-        <v>57310</v>
+        <v>91463</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5170,39 +5170,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>4745</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Hållängestjärnen, Ly lm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>641329</v>
+        <v>641089</v>
       </c>
       <c r="R42" t="n">
-        <v>7174806</v>
+        <v>7174407</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -5234,7 +5229,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5244,7 +5239,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5271,7 +5266,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>119536066</v>
+        <v>119536075</v>
       </c>
       <c r="B43" t="n">
         <v>57310</v>
@@ -5307,7 +5302,7 @@
       <c r="I43" t="inlineStr"/>
       <c r="M43" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
@@ -5316,10 +5311,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>641236</v>
+        <v>641329</v>
       </c>
       <c r="R43" t="n">
-        <v>7174632</v>
+        <v>7174806</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -5351,7 +5346,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5361,7 +5356,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5388,10 +5383,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>119536322</v>
+        <v>119536066</v>
       </c>
       <c r="B44" t="n">
-        <v>91856</v>
+        <v>57310</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5404,34 +5399,39 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>2059</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Hållängestjärnen, Ly lm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>641113</v>
+        <v>641236</v>
       </c>
       <c r="R44" t="n">
-        <v>7174347</v>
+        <v>7174632</v>
       </c>
       <c r="S44" t="n">
         <v>25</v>
@@ -5463,7 +5463,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5473,7 +5473,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6070,10 +6070,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>119536652</v>
+        <v>119536073</v>
       </c>
       <c r="B50" t="n">
-        <v>79607</v>
+        <v>57310</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6086,34 +6086,39 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Hållängestjärnen, Ly lm</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>641308</v>
+        <v>641246</v>
       </c>
       <c r="R50" t="n">
-        <v>7174808</v>
+        <v>7174787</v>
       </c>
       <c r="S50" t="n">
         <v>25</v>
@@ -6145,7 +6150,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6155,7 +6160,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6182,10 +6187,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>119536073</v>
+        <v>119535981</v>
       </c>
       <c r="B51" t="n">
-        <v>57310</v>
+        <v>58022</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6198,27 +6203,31 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>103056</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Videsparv</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Emberiza rustica</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
+          <t>Pallas, 1776</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>sträckande</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
@@ -6227,10 +6236,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>641246</v>
+        <v>640956</v>
       </c>
       <c r="R51" t="n">
-        <v>7174787</v>
+        <v>7174454</v>
       </c>
       <c r="S51" t="n">
         <v>25</v>
@@ -6262,7 +6271,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6272,7 +6281,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6299,10 +6308,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>119536245</v>
+        <v>119536652</v>
       </c>
       <c r="B52" t="n">
-        <v>91886</v>
+        <v>79607</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6311,25 +6320,25 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>232140</v>
+        <v>6458</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tajgataggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Phellodon secretus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Niemelä &amp; Kinnunen</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6339,10 +6348,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>641090</v>
+        <v>641308</v>
       </c>
       <c r="R52" t="n">
-        <v>7174359</v>
+        <v>7174808</v>
       </c>
       <c r="S52" t="n">
         <v>25</v>
@@ -6374,7 +6383,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6384,7 +6393,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6411,10 +6420,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>119535981</v>
+        <v>119536245</v>
       </c>
       <c r="B53" t="n">
-        <v>58022</v>
+        <v>91886</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6423,47 +6432,38 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>103056</v>
+        <v>232140</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Videsparv</t>
+          <t>Tajgataggsvamp</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Emberiza rustica</t>
+          <t>Phellodon secretus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Pallas, 1776</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>sträckande</t>
-        </is>
-      </c>
+          <t>Niemelä &amp; Kinnunen</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Hållängestjärnen, Ly lm</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>640956</v>
+        <v>641090</v>
       </c>
       <c r="R53" t="n">
-        <v>7174454</v>
+        <v>7174359</v>
       </c>
       <c r="S53" t="n">
         <v>25</v>
@@ -6495,7 +6495,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6505,7 +6505,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6873,10 +6873,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>119536064</v>
+        <v>119537104</v>
       </c>
       <c r="B57" t="n">
-        <v>57310</v>
+        <v>91840</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6885,43 +6885,38 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Hållängestjärnen, Ly lm</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>641165</v>
+        <v>640958</v>
       </c>
       <c r="R57" t="n">
-        <v>7174481</v>
+        <v>7174431</v>
       </c>
       <c r="S57" t="n">
         <v>25</v>
@@ -6953,7 +6948,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6963,7 +6958,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6990,7 +6985,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>119537104</v>
+        <v>119537110</v>
       </c>
       <c r="B58" t="n">
         <v>91840</v>
@@ -7030,10 +7025,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>640958</v>
+        <v>641215</v>
       </c>
       <c r="R58" t="n">
-        <v>7174431</v>
+        <v>7174693</v>
       </c>
       <c r="S58" t="n">
         <v>25</v>
@@ -7065,7 +7060,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7075,7 +7070,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7102,10 +7097,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>119537110</v>
+        <v>119536064</v>
       </c>
       <c r="B59" t="n">
-        <v>91840</v>
+        <v>57310</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7114,38 +7109,43 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Hållängestjärnen, Ly lm</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>641215</v>
+        <v>641165</v>
       </c>
       <c r="R59" t="n">
-        <v>7174693</v>
+        <v>7174481</v>
       </c>
       <c r="S59" t="n">
         <v>25</v>
@@ -7177,7 +7177,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7187,7 +7187,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AD59" t="b">

--- a/artfynd/A 59295-2023 artfynd.xlsx
+++ b/artfynd/A 59295-2023 artfynd.xlsx
@@ -1541,10 +1541,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119536065</v>
+        <v>119536320</v>
       </c>
       <c r="B10" t="n">
-        <v>57310</v>
+        <v>91856</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1557,39 +1557,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>2059</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Hållängestjärnen, Ly lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>641222</v>
+        <v>641092</v>
       </c>
       <c r="R10" t="n">
-        <v>7174563</v>
+        <v>7174408</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1621,7 +1616,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1631,7 +1626,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1658,10 +1653,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119536244</v>
+        <v>119536307</v>
       </c>
       <c r="B11" t="n">
-        <v>91886</v>
+        <v>91844</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1674,21 +1669,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>232140</v>
+        <v>4365</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tajgataggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellodon secretus</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Niemelä &amp; Kinnunen</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1733,7 +1728,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1743,7 +1738,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1770,10 +1765,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119536290</v>
+        <v>119536399</v>
       </c>
       <c r="B12" t="n">
-        <v>90509</v>
+        <v>56271</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1782,38 +1777,42 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>112</v>
+        <v>208255</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Skogsödla</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Zootoca vivipara</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Pat.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(Jacquin, 1787)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Hållängestjärnen, Ly lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>641323</v>
+        <v>641079</v>
       </c>
       <c r="R12" t="n">
-        <v>7174811</v>
+        <v>7174381</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1845,7 +1844,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1855,7 +1854,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1882,10 +1881,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119536694</v>
+        <v>119536264</v>
       </c>
       <c r="B13" t="n">
-        <v>79643</v>
+        <v>91884</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1894,25 +1893,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6464</v>
+        <v>5449</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1922,10 +1921,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>641286</v>
+        <v>641091</v>
       </c>
       <c r="R13" t="n">
-        <v>7174838</v>
+        <v>7174366</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1957,7 +1956,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1967,7 +1966,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1994,10 +1993,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119536076</v>
+        <v>119537111</v>
       </c>
       <c r="B14" t="n">
-        <v>57310</v>
+        <v>91840</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2006,43 +2005,38 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Hållängestjärnen, Ly lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>641327</v>
+        <v>641253</v>
       </c>
       <c r="R14" t="n">
-        <v>7174795</v>
+        <v>7174736</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2074,7 +2068,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2084,7 +2078,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2111,10 +2105,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119536118</v>
+        <v>119536613</v>
       </c>
       <c r="B15" t="n">
-        <v>91826</v>
+        <v>91832</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2127,21 +2121,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>3100</v>
+        <v>4361</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2151,10 +2145,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>641074</v>
+        <v>641113</v>
       </c>
       <c r="R15" t="n">
-        <v>7174409</v>
+        <v>7174348</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2186,7 +2180,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2196,7 +2190,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2223,10 +2217,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119536612</v>
+        <v>119536234</v>
       </c>
       <c r="B16" t="n">
-        <v>91832</v>
+        <v>91463</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2239,21 +2233,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4361</v>
+        <v>4745</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2263,10 +2257,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>641081</v>
+        <v>641099</v>
       </c>
       <c r="R16" t="n">
-        <v>7174380</v>
+        <v>7174354</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2298,7 +2292,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2308,7 +2302,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2335,10 +2329,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119537108</v>
+        <v>119536611</v>
       </c>
       <c r="B17" t="n">
-        <v>91840</v>
+        <v>91832</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2347,25 +2341,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2375,10 +2369,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>641238</v>
+        <v>641078</v>
       </c>
       <c r="R17" t="n">
-        <v>7174655</v>
+        <v>7174380</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2410,7 +2404,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2420,7 +2414,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2447,10 +2441,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119536320</v>
+        <v>119535996</v>
       </c>
       <c r="B18" t="n">
-        <v>91856</v>
+        <v>79115</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2463,21 +2457,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2059</v>
+        <v>229821</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2487,10 +2481,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>641092</v>
+        <v>640902</v>
       </c>
       <c r="R18" t="n">
-        <v>7174408</v>
+        <v>7174480</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2522,7 +2516,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2532,7 +2526,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2559,10 +2553,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119536070</v>
+        <v>119537105</v>
       </c>
       <c r="B19" t="n">
-        <v>57310</v>
+        <v>91840</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2571,43 +2565,38 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Hållängestjärnen, Ly lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>641226</v>
+        <v>640970</v>
       </c>
       <c r="R19" t="n">
-        <v>7174678</v>
+        <v>7174429</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2639,7 +2628,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2649,7 +2638,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2676,10 +2665,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119537244</v>
+        <v>119536069</v>
       </c>
       <c r="B20" t="n">
-        <v>91834</v>
+        <v>57310</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2692,34 +2681,39 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4362</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Hållängestjärnen, Ly lm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>641235</v>
+        <v>641236</v>
       </c>
       <c r="R20" t="n">
-        <v>7174629</v>
+        <v>7174679</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2751,7 +2745,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2761,7 +2755,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2788,10 +2782,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119536613</v>
+        <v>119536232</v>
       </c>
       <c r="B21" t="n">
-        <v>91832</v>
+        <v>91463</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2804,21 +2798,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4361</v>
+        <v>4745</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2828,10 +2822,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>641113</v>
+        <v>640989</v>
       </c>
       <c r="R21" t="n">
-        <v>7174348</v>
+        <v>7174436</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2863,7 +2857,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2873,7 +2867,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2900,10 +2894,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119536307</v>
+        <v>119536236</v>
       </c>
       <c r="B22" t="n">
-        <v>91844</v>
+        <v>91463</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2912,25 +2906,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4365</v>
+        <v>4745</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2940,10 +2934,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>641086</v>
+        <v>641255</v>
       </c>
       <c r="R22" t="n">
-        <v>7174359</v>
+        <v>7174732</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2975,7 +2969,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2985,7 +2979,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3012,10 +3006,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119536235</v>
+        <v>119536062</v>
       </c>
       <c r="B23" t="n">
-        <v>91463</v>
+        <v>57310</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3028,34 +3022,39 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4745</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Hållängestjärnen, Ly lm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>641229</v>
+        <v>641176</v>
       </c>
       <c r="R23" t="n">
-        <v>7174680</v>
+        <v>7174473</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3087,7 +3086,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3097,7 +3096,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3124,10 +3123,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119537105</v>
+        <v>119536692</v>
       </c>
       <c r="B24" t="n">
-        <v>91840</v>
+        <v>79643</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3140,21 +3139,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4364</v>
+        <v>6464</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3164,10 +3163,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>640970</v>
+        <v>641321</v>
       </c>
       <c r="R24" t="n">
-        <v>7174429</v>
+        <v>7174765</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3199,7 +3198,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3209,7 +3208,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3236,10 +3235,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119536264</v>
+        <v>119535981</v>
       </c>
       <c r="B25" t="n">
-        <v>91884</v>
+        <v>58022</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3252,34 +3251,43 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5449</v>
+        <v>103056</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Videsparv</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Emberiza rustica</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>Pallas, 1776</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>sträckande</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Hållängestjärnen, Ly lm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>641091</v>
+        <v>640956</v>
       </c>
       <c r="R25" t="n">
-        <v>7174366</v>
+        <v>7174454</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3311,7 +3319,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3321,7 +3329,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3348,10 +3356,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119535988</v>
+        <v>119536322</v>
       </c>
       <c r="B26" t="n">
-        <v>90527</v>
+        <v>91856</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3360,25 +3368,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5447</v>
+        <v>2059</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3388,10 +3396,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>641115</v>
+        <v>641113</v>
       </c>
       <c r="R26" t="n">
-        <v>7174359</v>
+        <v>7174347</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3423,7 +3431,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3433,7 +3441,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3460,10 +3468,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119535996</v>
+        <v>119535977</v>
       </c>
       <c r="B27" t="n">
-        <v>79115</v>
+        <v>74638</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3476,21 +3484,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>229821</v>
+        <v>6440</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3500,10 +3508,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>640902</v>
+        <v>641292</v>
       </c>
       <c r="R27" t="n">
-        <v>7174480</v>
+        <v>7174783</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3535,7 +3543,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3545,7 +3553,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3572,10 +3580,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119537243</v>
+        <v>119536233</v>
       </c>
       <c r="B28" t="n">
-        <v>91834</v>
+        <v>91463</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3588,21 +3596,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4362</v>
+        <v>4745</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3612,10 +3620,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>641074</v>
+        <v>641089</v>
       </c>
       <c r="R28" t="n">
-        <v>7174416</v>
+        <v>7174407</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3647,7 +3655,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3657,7 +3665,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3684,10 +3692,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119536232</v>
+        <v>119536118</v>
       </c>
       <c r="B29" t="n">
-        <v>91463</v>
+        <v>91826</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3700,21 +3708,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4745</v>
+        <v>3100</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Bankera fuligineoalba</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Schmidt : Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3724,10 +3732,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>640989</v>
+        <v>641074</v>
       </c>
       <c r="R29" t="n">
-        <v>7174436</v>
+        <v>7174409</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3759,7 +3767,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3769,7 +3777,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3796,10 +3804,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119536323</v>
+        <v>119537055</v>
       </c>
       <c r="B30" t="n">
-        <v>91856</v>
+        <v>78171</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3812,21 +3820,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2059</v>
+        <v>353</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3836,10 +3844,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>641250</v>
+        <v>641095</v>
       </c>
       <c r="R30" t="n">
-        <v>7174735</v>
+        <v>7174395</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3871,7 +3879,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3881,7 +3889,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3908,10 +3916,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119536399</v>
+        <v>119536308</v>
       </c>
       <c r="B31" t="n">
-        <v>56271</v>
+        <v>91844</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3920,42 +3928,38 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>208255</v>
+        <v>4365</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Skogsödla</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Zootoca vivipara</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Jacquin, 1787)</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(P.Karst) P.Karst</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Hållängestjärnen, Ly lm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>641079</v>
+        <v>641092</v>
       </c>
       <c r="R31" t="n">
-        <v>7174381</v>
+        <v>7174358</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -3987,7 +3991,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3997,7 +4001,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4024,10 +4028,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119536693</v>
+        <v>119537104</v>
       </c>
       <c r="B32" t="n">
-        <v>79643</v>
+        <v>91840</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4040,21 +4044,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6464</v>
+        <v>4364</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4064,10 +4068,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>641308</v>
+        <v>640958</v>
       </c>
       <c r="R32" t="n">
-        <v>7174808</v>
+        <v>7174431</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -4099,7 +4103,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4109,7 +4113,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4136,10 +4140,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119536611</v>
+        <v>119536119</v>
       </c>
       <c r="B33" t="n">
-        <v>91832</v>
+        <v>91826</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4152,21 +4156,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4361</v>
+        <v>3100</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Bankera fuligineoalba</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Schmidt : Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4176,10 +4180,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>641078</v>
+        <v>641091</v>
       </c>
       <c r="R33" t="n">
-        <v>7174380</v>
+        <v>7174366</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4211,7 +4215,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4221,7 +4225,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4248,10 +4252,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119536860</v>
+        <v>119535988</v>
       </c>
       <c r="B34" t="n">
-        <v>89252</v>
+        <v>90527</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4260,25 +4264,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6276</v>
+        <v>5447</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4288,10 +4292,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>641112</v>
+        <v>641115</v>
       </c>
       <c r="R34" t="n">
-        <v>7174348</v>
+        <v>7174359</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4323,7 +4327,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4333,7 +4337,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4360,10 +4364,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119536691</v>
+        <v>119536323</v>
       </c>
       <c r="B35" t="n">
-        <v>79643</v>
+        <v>91856</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4372,25 +4376,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6464</v>
+        <v>2059</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4400,10 +4404,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>641166</v>
+        <v>641250</v>
       </c>
       <c r="R35" t="n">
-        <v>7174471</v>
+        <v>7174735</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4435,7 +4439,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4445,7 +4449,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4472,7 +4476,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119536074</v>
+        <v>119536064</v>
       </c>
       <c r="B36" t="n">
         <v>57310</v>
@@ -4517,10 +4521,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>641316</v>
+        <v>641165</v>
       </c>
       <c r="R36" t="n">
-        <v>7174721</v>
+        <v>7174481</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4552,7 +4556,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4562,7 +4566,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4706,7 +4710,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119537107</v>
+        <v>119537109</v>
       </c>
       <c r="B38" t="n">
         <v>91840</v>
@@ -4746,10 +4750,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>641119</v>
+        <v>641236</v>
       </c>
       <c r="R38" t="n">
-        <v>7174434</v>
+        <v>7174680</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4781,7 +4785,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4791,7 +4795,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4818,10 +4822,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119536234</v>
+        <v>119536074</v>
       </c>
       <c r="B39" t="n">
-        <v>91463</v>
+        <v>57310</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4834,34 +4838,39 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>4745</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Hållängestjärnen, Ly lm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>641099</v>
+        <v>641316</v>
       </c>
       <c r="R39" t="n">
-        <v>7174354</v>
+        <v>7174721</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4893,7 +4902,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4903,7 +4912,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4930,10 +4939,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119537055</v>
+        <v>119536065</v>
       </c>
       <c r="B40" t="n">
-        <v>78171</v>
+        <v>57310</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4946,34 +4955,39 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>353</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Hållängestjärnen, Ly lm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>641095</v>
+        <v>641222</v>
       </c>
       <c r="R40" t="n">
-        <v>7174395</v>
+        <v>7174563</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -5005,7 +5019,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5015,7 +5029,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5042,10 +5056,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119536322</v>
+        <v>119536075</v>
       </c>
       <c r="B41" t="n">
-        <v>91856</v>
+        <v>57310</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5058,34 +5072,39 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>2059</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Hållängestjärnen, Ly lm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>641113</v>
+        <v>641329</v>
       </c>
       <c r="R41" t="n">
-        <v>7174347</v>
+        <v>7174806</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -5117,7 +5136,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5127,7 +5146,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5154,10 +5173,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>119536233</v>
+        <v>119536066</v>
       </c>
       <c r="B42" t="n">
-        <v>91463</v>
+        <v>57310</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5170,34 +5189,39 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>4745</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Hållängestjärnen, Ly lm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>641089</v>
+        <v>641236</v>
       </c>
       <c r="R42" t="n">
-        <v>7174407</v>
+        <v>7174632</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -5229,7 +5253,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5239,7 +5263,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5266,10 +5290,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>119536075</v>
+        <v>119537110</v>
       </c>
       <c r="B43" t="n">
-        <v>57310</v>
+        <v>91840</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5278,43 +5302,38 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Hållängestjärnen, Ly lm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>641329</v>
+        <v>641215</v>
       </c>
       <c r="R43" t="n">
-        <v>7174806</v>
+        <v>7174693</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -5346,7 +5365,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5356,7 +5375,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5383,10 +5402,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>119536066</v>
+        <v>119536235</v>
       </c>
       <c r="B44" t="n">
-        <v>57310</v>
+        <v>91463</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5399,39 +5418,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>4745</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Hållängestjärnen, Ly lm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>641236</v>
+        <v>641229</v>
       </c>
       <c r="R44" t="n">
-        <v>7174632</v>
+        <v>7174680</v>
       </c>
       <c r="S44" t="n">
         <v>25</v>
@@ -5463,7 +5477,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5473,7 +5487,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5500,7 +5514,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>119537109</v>
+        <v>119537103</v>
       </c>
       <c r="B45" t="n">
         <v>91840</v>
@@ -5540,10 +5554,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>641236</v>
+        <v>640944</v>
       </c>
       <c r="R45" t="n">
-        <v>7174680</v>
+        <v>7174428</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -5575,7 +5589,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5585,7 +5599,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5612,10 +5626,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>119536308</v>
+        <v>119536860</v>
       </c>
       <c r="B46" t="n">
-        <v>91844</v>
+        <v>89252</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5628,21 +5642,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>4365</v>
+        <v>6276</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5652,10 +5666,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>641092</v>
+        <v>641112</v>
       </c>
       <c r="R46" t="n">
-        <v>7174358</v>
+        <v>7174348</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -5687,7 +5701,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5697,7 +5711,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5724,7 +5738,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>119536068</v>
+        <v>119536076</v>
       </c>
       <c r="B47" t="n">
         <v>57310</v>
@@ -5769,10 +5783,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>641229</v>
+        <v>641327</v>
       </c>
       <c r="R47" t="n">
-        <v>7174680</v>
+        <v>7174795</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -5804,7 +5818,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5814,7 +5828,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5841,10 +5855,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>119535977</v>
+        <v>119536397</v>
       </c>
       <c r="B48" t="n">
-        <v>74638</v>
+        <v>79608</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5857,21 +5871,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6440</v>
+        <v>2081</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5881,10 +5895,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>641292</v>
+        <v>641310</v>
       </c>
       <c r="R48" t="n">
-        <v>7174783</v>
+        <v>7174818</v>
       </c>
       <c r="S48" t="n">
         <v>25</v>
@@ -5916,7 +5930,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5926,7 +5940,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5953,10 +5967,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>119536069</v>
+        <v>119536694</v>
       </c>
       <c r="B49" t="n">
-        <v>57310</v>
+        <v>79643</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5965,43 +5979,38 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Hållängestjärnen, Ly lm</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>641236</v>
+        <v>641286</v>
       </c>
       <c r="R49" t="n">
-        <v>7174679</v>
+        <v>7174838</v>
       </c>
       <c r="S49" t="n">
         <v>25</v>
@@ -6033,7 +6042,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6043,7 +6052,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6070,10 +6079,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>119536073</v>
+        <v>119536691</v>
       </c>
       <c r="B50" t="n">
-        <v>57310</v>
+        <v>79643</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6082,43 +6091,38 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Hållängestjärnen, Ly lm</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>641246</v>
+        <v>641166</v>
       </c>
       <c r="R50" t="n">
-        <v>7174787</v>
+        <v>7174471</v>
       </c>
       <c r="S50" t="n">
         <v>25</v>
@@ -6150,7 +6154,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6160,7 +6164,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6187,10 +6191,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>119535981</v>
+        <v>119536070</v>
       </c>
       <c r="B51" t="n">
-        <v>58022</v>
+        <v>57310</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6203,31 +6207,27 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>103056</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Videsparv</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Emberiza rustica</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Pallas, 1776</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="M51" t="inlineStr">
         <is>
-          <t>sträckande</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
@@ -6236,10 +6236,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>640956</v>
+        <v>641226</v>
       </c>
       <c r="R51" t="n">
-        <v>7174454</v>
+        <v>7174678</v>
       </c>
       <c r="S51" t="n">
         <v>25</v>
@@ -6271,7 +6271,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6281,7 +6281,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6308,10 +6308,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>119536652</v>
+        <v>119536321</v>
       </c>
       <c r="B52" t="n">
-        <v>79607</v>
+        <v>91856</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6324,21 +6324,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6458</v>
+        <v>2059</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6348,10 +6348,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>641308</v>
+        <v>641086</v>
       </c>
       <c r="R52" t="n">
-        <v>7174808</v>
+        <v>7174360</v>
       </c>
       <c r="S52" t="n">
         <v>25</v>
@@ -6383,7 +6383,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6393,7 +6393,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6420,10 +6420,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>119536245</v>
+        <v>119537244</v>
       </c>
       <c r="B53" t="n">
-        <v>91886</v>
+        <v>91834</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6432,25 +6432,25 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>232140</v>
+        <v>4362</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tajgataggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Phellodon secretus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Niemelä &amp; Kinnunen</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6460,10 +6460,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>641090</v>
+        <v>641235</v>
       </c>
       <c r="R53" t="n">
-        <v>7174359</v>
+        <v>7174629</v>
       </c>
       <c r="S53" t="n">
         <v>25</v>
@@ -6495,7 +6495,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6505,7 +6505,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6532,10 +6532,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>119536236</v>
+        <v>119537243</v>
       </c>
       <c r="B54" t="n">
-        <v>91463</v>
+        <v>91834</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6548,21 +6548,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>4745</v>
+        <v>4362</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6572,10 +6572,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>641255</v>
+        <v>641074</v>
       </c>
       <c r="R54" t="n">
-        <v>7174732</v>
+        <v>7174416</v>
       </c>
       <c r="S54" t="n">
         <v>25</v>
@@ -6607,7 +6607,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6617,7 +6617,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6644,10 +6644,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>119537111</v>
+        <v>119536071</v>
       </c>
       <c r="B55" t="n">
-        <v>91840</v>
+        <v>57310</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6656,38 +6656,43 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Hållängestjärnen, Ly lm</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>641253</v>
+        <v>641177</v>
       </c>
       <c r="R55" t="n">
-        <v>7174736</v>
+        <v>7174749</v>
       </c>
       <c r="S55" t="n">
         <v>25</v>
@@ -6719,7 +6724,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6729,7 +6734,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6756,10 +6761,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>119536062</v>
+        <v>119536244</v>
       </c>
       <c r="B56" t="n">
-        <v>57310</v>
+        <v>91886</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6768,43 +6773,38 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100109</v>
+        <v>232140</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tajgataggsvamp</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellodon secretus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Niemelä &amp; Kinnunen</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Hållängestjärnen, Ly lm</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>641176</v>
+        <v>641086</v>
       </c>
       <c r="R56" t="n">
-        <v>7174473</v>
+        <v>7174359</v>
       </c>
       <c r="S56" t="n">
         <v>25</v>
@@ -6836,7 +6836,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6846,7 +6846,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6873,10 +6873,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>119537104</v>
+        <v>119536290</v>
       </c>
       <c r="B57" t="n">
-        <v>91840</v>
+        <v>90509</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6885,25 +6885,25 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>4364</v>
+        <v>112</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6913,10 +6913,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>640958</v>
+        <v>641323</v>
       </c>
       <c r="R57" t="n">
-        <v>7174431</v>
+        <v>7174811</v>
       </c>
       <c r="S57" t="n">
         <v>25</v>
@@ -6948,7 +6948,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6958,7 +6958,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6985,10 +6985,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>119537110</v>
+        <v>119536652</v>
       </c>
       <c r="B58" t="n">
-        <v>91840</v>
+        <v>79607</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6997,25 +6997,25 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -7025,10 +7025,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>641215</v>
+        <v>641308</v>
       </c>
       <c r="R58" t="n">
-        <v>7174693</v>
+        <v>7174808</v>
       </c>
       <c r="S58" t="n">
         <v>25</v>
@@ -7060,7 +7060,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7070,7 +7070,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7097,10 +7097,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>119536064</v>
+        <v>119536612</v>
       </c>
       <c r="B59" t="n">
-        <v>57310</v>
+        <v>91832</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7113,39 +7113,34 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100109</v>
+        <v>4361</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Hållängestjärnen, Ly lm</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>641165</v>
+        <v>641081</v>
       </c>
       <c r="R59" t="n">
-        <v>7174481</v>
+        <v>7174380</v>
       </c>
       <c r="S59" t="n">
         <v>25</v>
@@ -7177,7 +7172,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7187,7 +7182,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7214,10 +7209,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>119536321</v>
+        <v>119537108</v>
       </c>
       <c r="B60" t="n">
-        <v>91856</v>
+        <v>91840</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7226,25 +7221,25 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>2059</v>
+        <v>4364</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7254,10 +7249,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>641086</v>
+        <v>641238</v>
       </c>
       <c r="R60" t="n">
-        <v>7174360</v>
+        <v>7174655</v>
       </c>
       <c r="S60" t="n">
         <v>25</v>
@@ -7289,7 +7284,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7299,7 +7294,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7326,10 +7321,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>119536119</v>
+        <v>119536245</v>
       </c>
       <c r="B61" t="n">
-        <v>91826</v>
+        <v>91886</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7338,25 +7333,25 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>3100</v>
+        <v>232140</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Tajgataggsvamp</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Phellodon secretus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
+          <t>Niemelä &amp; Kinnunen</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7366,10 +7361,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>641091</v>
+        <v>641090</v>
       </c>
       <c r="R61" t="n">
-        <v>7174366</v>
+        <v>7174359</v>
       </c>
       <c r="S61" t="n">
         <v>25</v>
@@ -7401,7 +7396,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7411,7 +7406,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7438,10 +7433,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>119536071</v>
+        <v>119536693</v>
       </c>
       <c r="B62" t="n">
-        <v>57310</v>
+        <v>79643</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7450,43 +7445,38 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Hållängestjärnen, Ly lm</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>641177</v>
+        <v>641308</v>
       </c>
       <c r="R62" t="n">
-        <v>7174749</v>
+        <v>7174808</v>
       </c>
       <c r="S62" t="n">
         <v>25</v>
@@ -7518,7 +7508,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7528,7 +7518,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7555,10 +7545,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>119536397</v>
+        <v>119537107</v>
       </c>
       <c r="B63" t="n">
-        <v>79608</v>
+        <v>91840</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7567,25 +7557,25 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>2081</v>
+        <v>4364</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7595,10 +7585,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>641310</v>
+        <v>641119</v>
       </c>
       <c r="R63" t="n">
-        <v>7174818</v>
+        <v>7174434</v>
       </c>
       <c r="S63" t="n">
         <v>25</v>
@@ -7630,7 +7620,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7640,7 +7630,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7667,10 +7657,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>119537103</v>
+        <v>119536068</v>
       </c>
       <c r="B64" t="n">
-        <v>91840</v>
+        <v>57310</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7679,38 +7669,43 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Hållängestjärnen, Ly lm</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>640944</v>
+        <v>641229</v>
       </c>
       <c r="R64" t="n">
-        <v>7174428</v>
+        <v>7174680</v>
       </c>
       <c r="S64" t="n">
         <v>25</v>
@@ -7742,7 +7737,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7752,7 +7747,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7779,10 +7774,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>119536692</v>
+        <v>119536073</v>
       </c>
       <c r="B65" t="n">
-        <v>79643</v>
+        <v>57310</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7791,38 +7786,43 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6464</v>
+        <v>100109</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Hållängestjärnen, Ly lm</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>641321</v>
+        <v>641246</v>
       </c>
       <c r="R65" t="n">
-        <v>7174765</v>
+        <v>7174787</v>
       </c>
       <c r="S65" t="n">
         <v>25</v>
@@ -7854,7 +7854,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7864,7 +7864,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD65" t="b">

--- a/artfynd/A 59295-2023 artfynd.xlsx
+++ b/artfynd/A 59295-2023 artfynd.xlsx
@@ -2553,10 +2553,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119537105</v>
+        <v>119536236</v>
       </c>
       <c r="B19" t="n">
-        <v>91840</v>
+        <v>91463</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2565,25 +2565,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4364</v>
+        <v>4745</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2593,10 +2593,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>640970</v>
+        <v>641255</v>
       </c>
       <c r="R19" t="n">
-        <v>7174429</v>
+        <v>7174732</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2628,7 +2628,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2638,7 +2638,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2665,10 +2665,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119536069</v>
+        <v>119537105</v>
       </c>
       <c r="B20" t="n">
-        <v>57310</v>
+        <v>91840</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2677,43 +2677,38 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Hållängestjärnen, Ly lm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>641236</v>
+        <v>640970</v>
       </c>
       <c r="R20" t="n">
-        <v>7174679</v>
+        <v>7174429</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2745,7 +2740,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2755,7 +2750,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2894,10 +2889,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119536236</v>
+        <v>119536069</v>
       </c>
       <c r="B22" t="n">
-        <v>91463</v>
+        <v>57310</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2910,34 +2905,39 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4745</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Hållängestjärnen, Ly lm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>641255</v>
+        <v>641236</v>
       </c>
       <c r="R22" t="n">
-        <v>7174732</v>
+        <v>7174679</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2969,7 +2969,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2979,7 +2979,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3006,10 +3006,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119536062</v>
+        <v>119536692</v>
       </c>
       <c r="B23" t="n">
-        <v>57310</v>
+        <v>79643</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3018,43 +3018,38 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Hållängestjärnen, Ly lm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>641176</v>
+        <v>641321</v>
       </c>
       <c r="R23" t="n">
-        <v>7174473</v>
+        <v>7174765</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3086,7 +3081,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3096,7 +3091,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3123,10 +3118,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119536692</v>
+        <v>119536062</v>
       </c>
       <c r="B24" t="n">
-        <v>79643</v>
+        <v>57310</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3135,38 +3130,43 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6464</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Hållängestjärnen, Ly lm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>641321</v>
+        <v>641176</v>
       </c>
       <c r="R24" t="n">
-        <v>7174765</v>
+        <v>7174473</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3198,7 +3198,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3208,7 +3208,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3356,10 +3356,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119536322</v>
+        <v>119535977</v>
       </c>
       <c r="B26" t="n">
-        <v>91856</v>
+        <v>74638</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3372,21 +3372,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2059</v>
+        <v>6440</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3396,10 +3396,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>641113</v>
+        <v>641292</v>
       </c>
       <c r="R26" t="n">
-        <v>7174347</v>
+        <v>7174783</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3431,7 +3431,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3441,7 +3441,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3468,10 +3468,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119535977</v>
+        <v>119536322</v>
       </c>
       <c r="B27" t="n">
-        <v>74638</v>
+        <v>91856</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3484,21 +3484,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6440</v>
+        <v>2059</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3508,10 +3508,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>641292</v>
+        <v>641113</v>
       </c>
       <c r="R27" t="n">
-        <v>7174783</v>
+        <v>7174347</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3543,7 +3543,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3553,7 +3553,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4140,10 +4140,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119536119</v>
+        <v>119536323</v>
       </c>
       <c r="B33" t="n">
-        <v>91826</v>
+        <v>91856</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4156,21 +4156,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>3100</v>
+        <v>2059</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4180,10 +4180,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>641091</v>
+        <v>641250</v>
       </c>
       <c r="R33" t="n">
-        <v>7174366</v>
+        <v>7174735</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4215,7 +4215,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4225,7 +4225,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4252,10 +4252,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119535988</v>
+        <v>119536119</v>
       </c>
       <c r="B34" t="n">
-        <v>90527</v>
+        <v>91826</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4264,25 +4264,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5447</v>
+        <v>3100</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Bankera fuligineoalba</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Schmidt : Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4292,10 +4292,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>641115</v>
+        <v>641091</v>
       </c>
       <c r="R34" t="n">
-        <v>7174359</v>
+        <v>7174366</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4327,7 +4327,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4337,7 +4337,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4364,10 +4364,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119536323</v>
+        <v>119535988</v>
       </c>
       <c r="B35" t="n">
-        <v>91856</v>
+        <v>90527</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4376,25 +4376,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>2059</v>
+        <v>5447</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4404,10 +4404,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>641250</v>
+        <v>641115</v>
       </c>
       <c r="R35" t="n">
-        <v>7174735</v>
+        <v>7174359</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4439,7 +4439,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4449,7 +4449,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -6873,10 +6873,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>119536290</v>
+        <v>119536612</v>
       </c>
       <c r="B57" t="n">
-        <v>90509</v>
+        <v>91832</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6889,21 +6889,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>112</v>
+        <v>4361</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6913,10 +6913,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>641323</v>
+        <v>641081</v>
       </c>
       <c r="R57" t="n">
-        <v>7174811</v>
+        <v>7174380</v>
       </c>
       <c r="S57" t="n">
         <v>25</v>
@@ -6948,7 +6948,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6958,7 +6958,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6985,10 +6985,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>119536652</v>
+        <v>119536290</v>
       </c>
       <c r="B58" t="n">
-        <v>79607</v>
+        <v>90509</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7001,21 +7001,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6458</v>
+        <v>112</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -7025,10 +7025,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>641308</v>
+        <v>641323</v>
       </c>
       <c r="R58" t="n">
-        <v>7174808</v>
+        <v>7174811</v>
       </c>
       <c r="S58" t="n">
         <v>25</v>
@@ -7060,7 +7060,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7070,7 +7070,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7097,10 +7097,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>119536612</v>
+        <v>119536652</v>
       </c>
       <c r="B59" t="n">
-        <v>91832</v>
+        <v>79607</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7113,21 +7113,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>4361</v>
+        <v>6458</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7137,10 +7137,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>641081</v>
+        <v>641308</v>
       </c>
       <c r="R59" t="n">
-        <v>7174380</v>
+        <v>7174808</v>
       </c>
       <c r="S59" t="n">
         <v>25</v>
@@ -7172,7 +7172,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7182,7 +7182,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AD59" t="b">

--- a/artfynd/A 59295-2023 artfynd.xlsx
+++ b/artfynd/A 59295-2023 artfynd.xlsx
@@ -1541,10 +1541,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119536320</v>
+        <v>119535996</v>
       </c>
       <c r="B10" t="n">
-        <v>91856</v>
+        <v>79115</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1557,21 +1557,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2059</v>
+        <v>229821</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1581,10 +1581,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>641092</v>
+        <v>640902</v>
       </c>
       <c r="R10" t="n">
-        <v>7174408</v>
+        <v>7174480</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1616,7 +1616,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1626,7 +1626,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1653,10 +1653,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119536307</v>
+        <v>119537055</v>
       </c>
       <c r="B11" t="n">
-        <v>91844</v>
+        <v>78171</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1665,25 +1665,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4365</v>
+        <v>353</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1693,10 +1693,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>641086</v>
+        <v>641095</v>
       </c>
       <c r="R11" t="n">
-        <v>7174359</v>
+        <v>7174395</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1728,7 +1728,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1738,7 +1738,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1765,10 +1765,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119536399</v>
+        <v>119536065</v>
       </c>
       <c r="B12" t="n">
-        <v>56271</v>
+        <v>57310</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1777,30 +1777,31 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>208255</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skogsödla</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Zootoca vivipara</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Jacquin, 1787)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1809,10 +1810,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>641079</v>
+        <v>641222</v>
       </c>
       <c r="R12" t="n">
-        <v>7174381</v>
+        <v>7174563</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1844,7 +1845,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1854,7 +1855,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1881,10 +1882,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119536264</v>
+        <v>119536323</v>
       </c>
       <c r="B13" t="n">
-        <v>91884</v>
+        <v>91856</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1897,21 +1898,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5449</v>
+        <v>2059</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1921,10 +1922,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>641091</v>
+        <v>641250</v>
       </c>
       <c r="R13" t="n">
-        <v>7174366</v>
+        <v>7174735</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1956,7 +1957,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1966,7 +1967,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1993,7 +1994,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119537111</v>
+        <v>119537108</v>
       </c>
       <c r="B14" t="n">
         <v>91840</v>
@@ -2033,10 +2034,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>641253</v>
+        <v>641238</v>
       </c>
       <c r="R14" t="n">
-        <v>7174736</v>
+        <v>7174655</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2068,7 +2069,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2078,7 +2079,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2105,10 +2106,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119536613</v>
+        <v>119536308</v>
       </c>
       <c r="B15" t="n">
-        <v>91832</v>
+        <v>91844</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2117,25 +2118,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4361</v>
+        <v>4365</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2145,10 +2146,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>641113</v>
+        <v>641092</v>
       </c>
       <c r="R15" t="n">
-        <v>7174348</v>
+        <v>7174358</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2180,7 +2181,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2190,7 +2191,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2217,7 +2218,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119536234</v>
+        <v>119536232</v>
       </c>
       <c r="B16" t="n">
         <v>91463</v>
@@ -2257,10 +2258,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>641099</v>
+        <v>640989</v>
       </c>
       <c r="R16" t="n">
-        <v>7174354</v>
+        <v>7174436</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2292,7 +2293,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2302,7 +2303,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2329,10 +2330,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119536611</v>
+        <v>119536691</v>
       </c>
       <c r="B17" t="n">
-        <v>91832</v>
+        <v>79643</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2341,25 +2342,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4361</v>
+        <v>6464</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2369,10 +2370,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>641078</v>
+        <v>641166</v>
       </c>
       <c r="R17" t="n">
-        <v>7174380</v>
+        <v>7174471</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2404,7 +2405,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2414,7 +2415,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2441,10 +2442,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119535996</v>
+        <v>119537104</v>
       </c>
       <c r="B18" t="n">
-        <v>79115</v>
+        <v>91840</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2453,25 +2454,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>229821</v>
+        <v>4364</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2481,10 +2482,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>640902</v>
+        <v>640958</v>
       </c>
       <c r="R18" t="n">
-        <v>7174480</v>
+        <v>7174431</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2516,7 +2517,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2526,7 +2527,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2553,10 +2554,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119536236</v>
+        <v>119535988</v>
       </c>
       <c r="B19" t="n">
-        <v>91463</v>
+        <v>90527</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2565,25 +2566,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4745</v>
+        <v>5447</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2593,10 +2594,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>641255</v>
+        <v>641115</v>
       </c>
       <c r="R19" t="n">
-        <v>7174732</v>
+        <v>7174359</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2628,7 +2629,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2638,7 +2639,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2665,10 +2666,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119537105</v>
+        <v>119536071</v>
       </c>
       <c r="B20" t="n">
-        <v>91840</v>
+        <v>57310</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2677,38 +2678,43 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Hållängestjärnen, Ly lm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>640970</v>
+        <v>641177</v>
       </c>
       <c r="R20" t="n">
-        <v>7174429</v>
+        <v>7174749</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2740,7 +2746,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2750,7 +2756,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2777,10 +2783,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119536232</v>
+        <v>119537244</v>
       </c>
       <c r="B21" t="n">
-        <v>91463</v>
+        <v>91834</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2793,21 +2799,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4745</v>
+        <v>4362</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2817,10 +2823,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>640989</v>
+        <v>641235</v>
       </c>
       <c r="R21" t="n">
-        <v>7174436</v>
+        <v>7174629</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2852,7 +2858,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2862,7 +2868,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2889,10 +2895,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119536069</v>
+        <v>119536652</v>
       </c>
       <c r="B22" t="n">
-        <v>57310</v>
+        <v>79607</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2905,39 +2911,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Hållängestjärnen, Ly lm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>641236</v>
+        <v>641308</v>
       </c>
       <c r="R22" t="n">
-        <v>7174679</v>
+        <v>7174808</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2969,7 +2970,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2979,7 +2980,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3006,7 +3007,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119536692</v>
+        <v>119536694</v>
       </c>
       <c r="B23" t="n">
         <v>79643</v>
@@ -3046,10 +3047,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>641321</v>
+        <v>641286</v>
       </c>
       <c r="R23" t="n">
-        <v>7174765</v>
+        <v>7174838</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3081,7 +3082,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3091,7 +3092,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3118,7 +3119,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119536062</v>
+        <v>119536064</v>
       </c>
       <c r="B24" t="n">
         <v>57310</v>
@@ -3163,10 +3164,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>641176</v>
+        <v>641165</v>
       </c>
       <c r="R24" t="n">
-        <v>7174473</v>
+        <v>7174481</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3235,10 +3236,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119535981</v>
+        <v>119536236</v>
       </c>
       <c r="B25" t="n">
-        <v>58022</v>
+        <v>91463</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3251,43 +3252,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>103056</v>
+        <v>4745</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Videsparv</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Emberiza rustica</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Pallas, 1776</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>sträckande</t>
-        </is>
-      </c>
+          <t>Fr.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Hållängestjärnen, Ly lm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>640956</v>
+        <v>641255</v>
       </c>
       <c r="R25" t="n">
-        <v>7174454</v>
+        <v>7174732</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3319,7 +3311,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3329,7 +3321,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3468,10 +3460,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119536322</v>
+        <v>119536062</v>
       </c>
       <c r="B27" t="n">
-        <v>91856</v>
+        <v>57310</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3484,34 +3476,39 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2059</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Hållängestjärnen, Ly lm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>641113</v>
+        <v>641176</v>
       </c>
       <c r="R27" t="n">
-        <v>7174347</v>
+        <v>7174473</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3543,7 +3540,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3553,7 +3550,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3580,10 +3577,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119536233</v>
+        <v>119536066</v>
       </c>
       <c r="B28" t="n">
-        <v>91463</v>
+        <v>57310</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3596,34 +3593,39 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4745</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Hållängestjärnen, Ly lm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>641089</v>
+        <v>641236</v>
       </c>
       <c r="R28" t="n">
-        <v>7174407</v>
+        <v>7174632</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3655,7 +3657,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3665,7 +3667,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3692,10 +3694,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119536118</v>
+        <v>119536264</v>
       </c>
       <c r="B29" t="n">
-        <v>91826</v>
+        <v>91884</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3708,21 +3710,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>3100</v>
+        <v>5449</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3732,10 +3734,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>641074</v>
+        <v>641091</v>
       </c>
       <c r="R29" t="n">
-        <v>7174409</v>
+        <v>7174366</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3767,7 +3769,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3777,7 +3779,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3804,10 +3806,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119537055</v>
+        <v>119535981</v>
       </c>
       <c r="B30" t="n">
-        <v>78171</v>
+        <v>58022</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3820,34 +3822,43 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>353</v>
+        <v>103056</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Videsparv</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Emberiza rustica</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>Pallas, 1776</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>sträckande</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Hållängestjärnen, Ly lm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>641095</v>
+        <v>640956</v>
       </c>
       <c r="R30" t="n">
-        <v>7174395</v>
+        <v>7174454</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3879,7 +3890,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3889,7 +3900,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3916,10 +3927,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119536308</v>
+        <v>119536118</v>
       </c>
       <c r="B31" t="n">
-        <v>91844</v>
+        <v>91826</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3928,25 +3939,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4365</v>
+        <v>3100</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Bankera fuligineoalba</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Schmidt : Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3956,10 +3967,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>641092</v>
+        <v>641074</v>
       </c>
       <c r="R31" t="n">
-        <v>7174358</v>
+        <v>7174409</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -3991,7 +4002,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4001,7 +4012,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4028,10 +4039,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119537104</v>
+        <v>119536397</v>
       </c>
       <c r="B32" t="n">
-        <v>91840</v>
+        <v>79608</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4040,25 +4051,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4364</v>
+        <v>2081</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4068,10 +4079,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>640958</v>
+        <v>641310</v>
       </c>
       <c r="R32" t="n">
-        <v>7174431</v>
+        <v>7174818</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -4103,7 +4114,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4113,7 +4124,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4140,7 +4151,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119536323</v>
+        <v>119536321</v>
       </c>
       <c r="B33" t="n">
         <v>91856</v>
@@ -4180,10 +4191,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>641250</v>
+        <v>641086</v>
       </c>
       <c r="R33" t="n">
-        <v>7174735</v>
+        <v>7174360</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4215,7 +4226,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4225,7 +4236,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4252,10 +4263,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119536119</v>
+        <v>119536320</v>
       </c>
       <c r="B34" t="n">
-        <v>91826</v>
+        <v>91856</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4268,21 +4279,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>3100</v>
+        <v>2059</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4292,10 +4303,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>641091</v>
+        <v>641092</v>
       </c>
       <c r="R34" t="n">
-        <v>7174366</v>
+        <v>7174408</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4327,7 +4338,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4337,7 +4348,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4364,10 +4375,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119535988</v>
+        <v>119537103</v>
       </c>
       <c r="B35" t="n">
-        <v>90527</v>
+        <v>91840</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4380,21 +4391,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5447</v>
+        <v>4364</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4404,10 +4415,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>641115</v>
+        <v>640944</v>
       </c>
       <c r="R35" t="n">
-        <v>7174359</v>
+        <v>7174428</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4439,7 +4450,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4449,7 +4460,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4476,7 +4487,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119536064</v>
+        <v>119536074</v>
       </c>
       <c r="B36" t="n">
         <v>57310</v>
@@ -4521,10 +4532,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>641165</v>
+        <v>641316</v>
       </c>
       <c r="R36" t="n">
-        <v>7174481</v>
+        <v>7174721</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4556,7 +4567,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4566,7 +4577,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4593,10 +4604,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119536067</v>
+        <v>119536244</v>
       </c>
       <c r="B37" t="n">
-        <v>57310</v>
+        <v>91886</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4605,43 +4616,38 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>232140</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tajgataggsvamp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellodon secretus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Niemelä &amp; Kinnunen</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Hållängestjärnen, Ly lm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>641236</v>
+        <v>641086</v>
       </c>
       <c r="R37" t="n">
-        <v>7174680</v>
+        <v>7174359</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4673,7 +4679,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4683,7 +4689,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4710,10 +4716,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119537109</v>
+        <v>119537243</v>
       </c>
       <c r="B38" t="n">
-        <v>91840</v>
+        <v>91834</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4722,25 +4728,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4750,10 +4756,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>641236</v>
+        <v>641074</v>
       </c>
       <c r="R38" t="n">
-        <v>7174680</v>
+        <v>7174416</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4785,7 +4791,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4795,7 +4801,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4822,10 +4828,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119536074</v>
+        <v>119536307</v>
       </c>
       <c r="B39" t="n">
-        <v>57310</v>
+        <v>91844</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4834,43 +4840,38 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>4365</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Hållängestjärnen, Ly lm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>641316</v>
+        <v>641086</v>
       </c>
       <c r="R39" t="n">
-        <v>7174721</v>
+        <v>7174359</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4902,7 +4903,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4912,7 +4913,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4939,7 +4940,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119536065</v>
+        <v>119536067</v>
       </c>
       <c r="B40" t="n">
         <v>57310</v>
@@ -4984,10 +4985,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>641222</v>
+        <v>641236</v>
       </c>
       <c r="R40" t="n">
-        <v>7174563</v>
+        <v>7174680</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -5019,7 +5020,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5029,7 +5030,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5056,7 +5057,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119536075</v>
+        <v>119536073</v>
       </c>
       <c r="B41" t="n">
         <v>57310</v>
@@ -5092,7 +5093,7 @@
       <c r="I41" t="inlineStr"/>
       <c r="M41" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
@@ -5101,10 +5102,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>641329</v>
+        <v>641246</v>
       </c>
       <c r="R41" t="n">
-        <v>7174806</v>
+        <v>7174787</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -5136,7 +5137,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5146,7 +5147,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5173,10 +5174,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>119536066</v>
+        <v>119536119</v>
       </c>
       <c r="B42" t="n">
-        <v>57310</v>
+        <v>91826</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5189,39 +5190,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>3100</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bankera fuligineoalba</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schmidt : Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Hållängestjärnen, Ly lm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>641236</v>
+        <v>641091</v>
       </c>
       <c r="R42" t="n">
-        <v>7174632</v>
+        <v>7174366</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -5253,7 +5249,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5263,7 +5259,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5290,7 +5286,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>119537110</v>
+        <v>119537111</v>
       </c>
       <c r="B43" t="n">
         <v>91840</v>
@@ -5330,10 +5326,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>641215</v>
+        <v>641253</v>
       </c>
       <c r="R43" t="n">
-        <v>7174693</v>
+        <v>7174736</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -5365,7 +5361,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5375,7 +5371,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5402,10 +5398,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>119536235</v>
+        <v>119537105</v>
       </c>
       <c r="B44" t="n">
-        <v>91463</v>
+        <v>91840</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5414,25 +5410,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>4745</v>
+        <v>4364</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5442,10 +5438,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>641229</v>
+        <v>640970</v>
       </c>
       <c r="R44" t="n">
-        <v>7174680</v>
+        <v>7174429</v>
       </c>
       <c r="S44" t="n">
         <v>25</v>
@@ -5477,7 +5473,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5487,7 +5483,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5514,7 +5510,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>119537103</v>
+        <v>119537109</v>
       </c>
       <c r="B45" t="n">
         <v>91840</v>
@@ -5554,10 +5550,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>640944</v>
+        <v>641236</v>
       </c>
       <c r="R45" t="n">
-        <v>7174428</v>
+        <v>7174680</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -5589,7 +5585,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5599,7 +5595,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5626,10 +5622,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>119536860</v>
+        <v>119536611</v>
       </c>
       <c r="B46" t="n">
-        <v>89252</v>
+        <v>91832</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5638,25 +5634,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6276</v>
+        <v>4361</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5666,10 +5662,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>641112</v>
+        <v>641078</v>
       </c>
       <c r="R46" t="n">
-        <v>7174348</v>
+        <v>7174380</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -5701,7 +5697,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5711,7 +5707,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5738,7 +5734,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>119536076</v>
+        <v>119536070</v>
       </c>
       <c r="B47" t="n">
         <v>57310</v>
@@ -5774,7 +5770,7 @@
       <c r="I47" t="inlineStr"/>
       <c r="M47" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -5783,10 +5779,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>641327</v>
+        <v>641226</v>
       </c>
       <c r="R47" t="n">
-        <v>7174795</v>
+        <v>7174678</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -5818,7 +5814,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5828,7 +5824,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5855,10 +5851,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>119536397</v>
+        <v>119536245</v>
       </c>
       <c r="B48" t="n">
-        <v>79608</v>
+        <v>91886</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5867,25 +5863,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>2081</v>
+        <v>232140</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tajgataggsvamp</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellodon secretus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>Niemelä &amp; Kinnunen</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5895,10 +5891,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>641310</v>
+        <v>641090</v>
       </c>
       <c r="R48" t="n">
-        <v>7174818</v>
+        <v>7174359</v>
       </c>
       <c r="S48" t="n">
         <v>25</v>
@@ -5930,7 +5926,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5940,7 +5936,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5967,10 +5963,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>119536694</v>
+        <v>119536233</v>
       </c>
       <c r="B49" t="n">
-        <v>79643</v>
+        <v>91463</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5979,25 +5975,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6464</v>
+        <v>4745</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6007,10 +6003,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>641286</v>
+        <v>641089</v>
       </c>
       <c r="R49" t="n">
-        <v>7174838</v>
+        <v>7174407</v>
       </c>
       <c r="S49" t="n">
         <v>25</v>
@@ -6042,7 +6038,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6052,7 +6048,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6079,10 +6075,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>119536691</v>
+        <v>119536613</v>
       </c>
       <c r="B50" t="n">
-        <v>79643</v>
+        <v>91832</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6091,25 +6087,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6464</v>
+        <v>4361</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6119,10 +6115,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>641166</v>
+        <v>641113</v>
       </c>
       <c r="R50" t="n">
-        <v>7174471</v>
+        <v>7174348</v>
       </c>
       <c r="S50" t="n">
         <v>25</v>
@@ -6154,7 +6150,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6164,7 +6160,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6191,10 +6187,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>119536070</v>
+        <v>119536322</v>
       </c>
       <c r="B51" t="n">
-        <v>57310</v>
+        <v>91856</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6207,39 +6203,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>2059</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Hållängestjärnen, Ly lm</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>641226</v>
+        <v>641113</v>
       </c>
       <c r="R51" t="n">
-        <v>7174678</v>
+        <v>7174347</v>
       </c>
       <c r="S51" t="n">
         <v>25</v>
@@ -6271,7 +6262,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6281,7 +6272,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6308,10 +6299,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>119536321</v>
+        <v>119536290</v>
       </c>
       <c r="B52" t="n">
-        <v>91856</v>
+        <v>90509</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6324,21 +6315,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>2059</v>
+        <v>112</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6348,10 +6339,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>641086</v>
+        <v>641323</v>
       </c>
       <c r="R52" t="n">
-        <v>7174360</v>
+        <v>7174811</v>
       </c>
       <c r="S52" t="n">
         <v>25</v>
@@ -6383,7 +6374,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6393,7 +6384,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6420,10 +6411,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>119537244</v>
+        <v>119536612</v>
       </c>
       <c r="B53" t="n">
-        <v>91834</v>
+        <v>91832</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6436,21 +6427,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>4362</v>
+        <v>4361</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6460,10 +6451,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>641235</v>
+        <v>641081</v>
       </c>
       <c r="R53" t="n">
-        <v>7174629</v>
+        <v>7174380</v>
       </c>
       <c r="S53" t="n">
         <v>25</v>
@@ -6495,7 +6486,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6505,7 +6496,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6532,10 +6523,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>119537243</v>
+        <v>119537110</v>
       </c>
       <c r="B54" t="n">
-        <v>91834</v>
+        <v>91840</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6544,25 +6535,25 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6572,10 +6563,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>641074</v>
+        <v>641215</v>
       </c>
       <c r="R54" t="n">
-        <v>7174416</v>
+        <v>7174693</v>
       </c>
       <c r="S54" t="n">
         <v>25</v>
@@ -6607,7 +6598,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6617,7 +6608,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6644,10 +6635,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>119536071</v>
+        <v>119536692</v>
       </c>
       <c r="B55" t="n">
-        <v>57310</v>
+        <v>79643</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6656,43 +6647,38 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Hållängestjärnen, Ly lm</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>641177</v>
+        <v>641321</v>
       </c>
       <c r="R55" t="n">
-        <v>7174749</v>
+        <v>7174765</v>
       </c>
       <c r="S55" t="n">
         <v>25</v>
@@ -6724,7 +6710,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6734,7 +6720,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6761,10 +6747,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>119536244</v>
+        <v>119536399</v>
       </c>
       <c r="B56" t="n">
-        <v>91886</v>
+        <v>56271</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6773,38 +6759,42 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>232140</v>
+        <v>208255</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tajgataggsvamp</t>
+          <t>Skogsödla</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Phellodon secretus</t>
+          <t>Zootoca vivipara</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Niemelä &amp; Kinnunen</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
+          <t>(Jacquin, 1787)</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Hållängestjärnen, Ly lm</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>641086</v>
+        <v>641079</v>
       </c>
       <c r="R56" t="n">
-        <v>7174359</v>
+        <v>7174381</v>
       </c>
       <c r="S56" t="n">
         <v>25</v>
@@ -6836,7 +6826,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6846,7 +6836,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6873,10 +6863,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>119536612</v>
+        <v>119536069</v>
       </c>
       <c r="B57" t="n">
-        <v>91832</v>
+        <v>57310</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6889,34 +6879,39 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>4361</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Hållängestjärnen, Ly lm</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>641081</v>
+        <v>641236</v>
       </c>
       <c r="R57" t="n">
-        <v>7174380</v>
+        <v>7174679</v>
       </c>
       <c r="S57" t="n">
         <v>25</v>
@@ -6948,7 +6943,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6958,7 +6953,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6985,10 +6980,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>119536290</v>
+        <v>119536076</v>
       </c>
       <c r="B58" t="n">
-        <v>90509</v>
+        <v>57310</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7001,34 +6996,39 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>112</v>
+        <v>100109</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Hållängestjärnen, Ly lm</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>641323</v>
+        <v>641327</v>
       </c>
       <c r="R58" t="n">
-        <v>7174811</v>
+        <v>7174795</v>
       </c>
       <c r="S58" t="n">
         <v>25</v>
@@ -7060,7 +7060,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7070,7 +7070,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7097,10 +7097,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>119536652</v>
+        <v>119536068</v>
       </c>
       <c r="B59" t="n">
-        <v>79607</v>
+        <v>57310</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7113,34 +7113,39 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Hållängestjärnen, Ly lm</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>641308</v>
+        <v>641229</v>
       </c>
       <c r="R59" t="n">
-        <v>7174808</v>
+        <v>7174680</v>
       </c>
       <c r="S59" t="n">
         <v>25</v>
@@ -7172,7 +7177,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7182,7 +7187,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7209,7 +7214,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>119537108</v>
+        <v>119537107</v>
       </c>
       <c r="B60" t="n">
         <v>91840</v>
@@ -7249,10 +7254,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>641238</v>
+        <v>641119</v>
       </c>
       <c r="R60" t="n">
-        <v>7174655</v>
+        <v>7174434</v>
       </c>
       <c r="S60" t="n">
         <v>25</v>
@@ -7284,7 +7289,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7294,7 +7299,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7321,10 +7326,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>119536245</v>
+        <v>119536075</v>
       </c>
       <c r="B61" t="n">
-        <v>91886</v>
+        <v>57310</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7333,38 +7338,43 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>232140</v>
+        <v>100109</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tajgataggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Phellodon secretus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Niemelä &amp; Kinnunen</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Hållängestjärnen, Ly lm</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>641090</v>
+        <v>641329</v>
       </c>
       <c r="R61" t="n">
-        <v>7174359</v>
+        <v>7174806</v>
       </c>
       <c r="S61" t="n">
         <v>25</v>
@@ -7396,7 +7406,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7406,7 +7416,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7433,10 +7443,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>119536693</v>
+        <v>119536235</v>
       </c>
       <c r="B62" t="n">
-        <v>79643</v>
+        <v>91463</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7445,25 +7455,25 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6464</v>
+        <v>4745</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7473,10 +7483,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>641308</v>
+        <v>641229</v>
       </c>
       <c r="R62" t="n">
-        <v>7174808</v>
+        <v>7174680</v>
       </c>
       <c r="S62" t="n">
         <v>25</v>
@@ -7508,7 +7518,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7518,7 +7528,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7545,10 +7555,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>119537107</v>
+        <v>119536234</v>
       </c>
       <c r="B63" t="n">
-        <v>91840</v>
+        <v>91463</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7557,25 +7567,25 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>4364</v>
+        <v>4745</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7585,10 +7595,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>641119</v>
+        <v>641099</v>
       </c>
       <c r="R63" t="n">
-        <v>7174434</v>
+        <v>7174354</v>
       </c>
       <c r="S63" t="n">
         <v>25</v>
@@ -7620,7 +7630,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7630,7 +7640,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7657,10 +7667,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>119536068</v>
+        <v>119536693</v>
       </c>
       <c r="B64" t="n">
-        <v>57310</v>
+        <v>79643</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7669,43 +7679,38 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Hållängestjärnen, Ly lm</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>641229</v>
+        <v>641308</v>
       </c>
       <c r="R64" t="n">
-        <v>7174680</v>
+        <v>7174808</v>
       </c>
       <c r="S64" t="n">
         <v>25</v>
@@ -7737,7 +7742,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7747,7 +7752,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7774,10 +7779,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>119536073</v>
+        <v>119536860</v>
       </c>
       <c r="B65" t="n">
-        <v>57310</v>
+        <v>89252</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7786,43 +7791,38 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100109</v>
+        <v>6276</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Hållängestjärnen, Ly lm</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>641246</v>
+        <v>641112</v>
       </c>
       <c r="R65" t="n">
-        <v>7174787</v>
+        <v>7174348</v>
       </c>
       <c r="S65" t="n">
         <v>25</v>
@@ -7854,7 +7854,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7864,7 +7864,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD65" t="b">

--- a/artfynd/A 59295-2023 artfynd.xlsx
+++ b/artfynd/A 59295-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY65"/>
+  <dimension ref="A1:AY66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7889,6 +7889,120 @@
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>122586710</v>
+      </c>
+      <c r="B66" t="n">
+        <v>57536</v>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Vinliden, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>641259</v>
+      </c>
+      <c r="R66" t="n">
+        <v>7174736</v>
+      </c>
+      <c r="S66" t="n">
+        <v>10</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2025-02-12</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2025-02-12</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Christer Johansson</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Greger Thorsson</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 59295-2023 artfynd.xlsx
+++ b/artfynd/A 59295-2023 artfynd.xlsx
@@ -7894,7 +7894,7 @@
         <v>122586710</v>
       </c>
       <c r="B66" t="n">
-        <v>57536</v>
+        <v>57537</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>

--- a/artfynd/A 59295-2023 artfynd.xlsx
+++ b/artfynd/A 59295-2023 artfynd.xlsx
@@ -7894,7 +7894,7 @@
         <v>122586710</v>
       </c>
       <c r="B66" t="n">
-        <v>57537</v>
+        <v>57631</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
